--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,327 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129996515</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80190</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>475423</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6831611</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129996512</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78842</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>475420</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6831551</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129996513</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>475420</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831551</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>129996515</v>
       </c>
       <c r="B12" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129996512</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129996513</v>
       </c>
       <c r="B14" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>129996515</v>
       </c>
       <c r="B12" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129996512</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129996513</v>
       </c>
       <c r="B14" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>129996515</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129996512</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129996513</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>129996515</v>
       </c>
       <c r="B12" t="n">
-        <v>80201</v>
+        <v>80286</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129996512</v>
       </c>
       <c r="B13" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129996513</v>
       </c>
       <c r="B14" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127387345</v>
+        <v>127389297</v>
       </c>
       <c r="B2" t="n">
-        <v>78787</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475336</v>
+        <v>475300</v>
       </c>
       <c r="R2" t="n">
-        <v>6831509</v>
+        <v>6831465</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127387334</v>
+        <v>129996515</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475332</v>
+        <v>475423</v>
       </c>
       <c r="R3" t="n">
-        <v>6831515</v>
+        <v>6831611</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,68 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127405583</v>
+        <v>127384584</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475343</v>
+        <v>475308</v>
       </c>
       <c r="R4" t="n">
-        <v>6831440</v>
+        <v>6831502</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,12 +964,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Damne, Alexander Ahl, Alice Helander, Elias Blad, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Tilde Carlinger</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -977,11 +979,11 @@
         <v>127386377</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1071,14 +1073,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127387353</v>
+        <v>127386944</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1106,13 +1108,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475327</v>
+        <v>475306</v>
       </c>
       <c r="R6" t="n">
-        <v>6831522</v>
+        <v>6831463</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,26 +1158,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Emilia Blixt, Malte Lindberg, Nadja Karlsson, Erik Christiansson, Elias Blad, Sofia Damne, Filippa Paperin, Elis Lewin, Ivar Anderberg, Alexander Ahl, Karla Alfaro Gripe, Tilde Carlinger, Alice Helander, Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127386944</v>
+        <v>127387353</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1203,13 +1205,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475306</v>
+        <v>475327</v>
       </c>
       <c r="R7" t="n">
-        <v>6831463</v>
+        <v>6831522</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emilia Blixt, Malte Lindberg, Nadja Karlsson, Erik Christiansson, Elias Blad, Sofia Damne, Filippa Paperin, Elis Lewin, Ivar Anderberg, Alexander Ahl, Karla Alfaro Gripe, Tilde Carlinger, Alice Helander, Karin Berg Andersson</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127387328</v>
+        <v>127389457</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1300,13 +1302,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475326</v>
+        <v>475277</v>
       </c>
       <c r="R8" t="n">
-        <v>6831506</v>
+        <v>6831448</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,44 +1352,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127405615</v>
+        <v>127387345</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475343</v>
+        <v>475336</v>
       </c>
       <c r="R9" t="n">
-        <v>6831438</v>
+        <v>6831509</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1441,29 +1443,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sofia Damne, Alexander Ahl, Alice Helander, Elias Blad, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Tilde Carlinger</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127384584</v>
+        <v>129996513</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475308</v>
+        <v>475420</v>
       </c>
       <c r="R10" t="n">
-        <v>6831502</v>
+        <v>6831551</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1525,12 +1526,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1545,22 +1556,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127387335</v>
+        <v>130041508</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,13 +1603,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475340</v>
+        <v>475485</v>
       </c>
       <c r="R11" t="n">
-        <v>6831507</v>
+        <v>6831411</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1622,12 +1633,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1642,22 +1663,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129996515</v>
+        <v>127387328</v>
       </c>
       <c r="B12" t="n">
-        <v>80286</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,13 +1710,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475423</v>
+        <v>475326</v>
       </c>
       <c r="R12" t="n">
-        <v>6831611</v>
+        <v>6831506</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1719,22 +1740,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1749,22 +1760,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129996512</v>
+        <v>130041435</v>
       </c>
       <c r="B13" t="n">
-        <v>78938</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475420</v>
+        <v>475485</v>
       </c>
       <c r="R13" t="n">
-        <v>6831551</v>
+        <v>6831413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1826,22 +1837,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1861,17 +1872,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129996513</v>
+        <v>130044586</v>
       </c>
       <c r="B14" t="n">
-        <v>78937</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,34 +1890,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475420</v>
+        <v>475506</v>
       </c>
       <c r="R14" t="n">
-        <v>6831551</v>
+        <v>6831387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,22 +1947,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1957,21 +1961,1332 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130044587</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127405583</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475343</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6831440</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sofia Damne, Alexander Ahl, Alice Helander, Elias Blad, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127405615</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>475343</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6831438</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sofia Damne, Alexander Ahl, Alice Helander, Elias Blad, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karla Alfaro Gripe, Malte Lindberg, Nadja Karlsson, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127386368</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>475330</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831400</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Christiansson, Elias Blad, Filippa Paperin, Karin Berg Andersson, Karla Alfaro Gripe, Malte Lindberg, Sofia Damne, Alice Helander, Emilia Blixt, Tilde Carlinger, Nadja Karlsson, Alexander Ahl, Ivar Anderberg, Elis Lewin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127387334</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>475332</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831515</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127387335</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>475340</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6831507</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127389370</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>475277</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6831448</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129996512</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>475420</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6831551</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130041492</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>475485</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6831411</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130044584</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>475500</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6831409</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130044585</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>475506</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831387</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130044604</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130044601</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53690-2025 artfynd.xlsx
+++ b/artfynd/A 53690-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384584</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386377</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386944</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387353</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389457</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387345</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996513</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041508</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387328</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041435</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044586</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044587</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405583</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2281,6 +2361,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405615</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2378,6 +2463,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386368</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2475,6 +2565,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387334</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2572,6 +2667,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387335</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389370</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2776,6 +2881,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996512</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041492</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,6 +3099,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044584</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3085,6 +3205,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044585</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3186,6 +3311,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044604</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3287,8 +3417,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>